--- a/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_HESTIA MENORCA.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_HESTIA MENORCA.xlsx
@@ -565,13 +565,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>9.746700000000001</v>
+        <v>9.614599999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9842</v>
+        <v>9.408000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2375</v>
+        <v>0.2066</v>
       </c>
       <c r="G2" t="n">
         <v>4.1204</v>
@@ -610,13 +610,13 @@
         <v>9.4718</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5705</v>
+        <v>-0.7027000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7255</v>
+        <v>0.1493</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.296</v>
+        <v>-0.852</v>
       </c>
       <c r="V2" t="n">
         <v>-0.4114000000000001</v>
@@ -643,13 +643,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5779</v>
+        <v>3.5103</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0187</v>
+        <v>1.1454</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5591</v>
+        <v>2.3647</v>
       </c>
       <c r="G3" t="n">
         <v>4.0424</v>
@@ -688,13 +688,13 @@
         <v>5.2866</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0111</v>
+        <v>-0.05650000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6825000000000001</v>
+        <v>-0.1907999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3286</v>
+        <v>0.1344</v>
       </c>
       <c r="V3" t="n">
         <v>-4.2202</v>
@@ -721,13 +721,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04679999999999973</v>
+        <v>1.6796</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6014</v>
+        <v>3.7199</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.5547</v>
+        <v>-2.0404</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3798000000000001</v>
@@ -766,13 +766,13 @@
         <v>7.4893</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.7493</v>
+        <v>-1.1165</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5439</v>
+        <v>-0.4253</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2054</v>
+        <v>-0.6912</v>
       </c>
       <c r="V4" t="n">
         <v>6.039400000000001</v>
@@ -799,13 +799,13 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3504</v>
+        <v>-0.2927</v>
       </c>
       <c r="E5" t="n">
         <v>0.7131000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0634</v>
+        <v>-1.0058</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3247</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.02559999999999998</v>
+        <v>0.03200000000000003</v>
       </c>
       <c r="T5" t="n">
         <v>0.02810000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.05380000000000001</v>
+        <v>0.003900000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.4889</v>
+        <v>-0.6504999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.177899999999999</v>
+        <v>-3.1861</v>
       </c>
       <c r="F6" t="n">
-        <v>2.689</v>
+        <v>2.5356</v>
       </c>
       <c r="G6" t="n">
         <v>-3.4469</v>
@@ -922,13 +922,13 @@
         <v>6.3879</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.4635</v>
+        <v>-1.6252</v>
       </c>
       <c r="T6" t="n">
-        <v>-4.0792</v>
+        <v>-2.0874</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6159</v>
+        <v>0.4625</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5259</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.8793</v>
+        <v>-3.5749</v>
       </c>
       <c r="E7" t="n">
-        <v>3.004100000000001</v>
+        <v>-4.572500000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.8834</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1061000000000005</v>
+        <v>5.667</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5507</v>
+        <v>-4.137600000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.4447</v>
+        <v>9.804600000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8843</v>
+        <v>9.7738</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2477</v>
+        <v>-3.5013</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3634</v>
+        <v>13.2751</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7782</v>
+        <v>-4.1067</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6969999999999998</v>
+        <v>-0.6363</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0813</v>
+        <v>-3.4705</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3216</v>
+        <v>-6.6082</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.5069</v>
+        <v>-14.7582</v>
       </c>
       <c r="R7" t="n">
-        <v>4.1852</v>
+        <v>8.1502</v>
       </c>
       <c r="S7" t="n">
-        <v>3.0058</v>
+        <v>-1.588</v>
       </c>
       <c r="T7" t="n">
-        <v>4.3316</v>
+        <v>-1.0768</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.3258</v>
+        <v>-0.5111</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.6695</v>
+        <v>-1.0458</v>
       </c>
       <c r="W7" t="n">
-        <v>1.295</v>
+        <v>1.4889</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.9645</v>
+        <v>-2.5347</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.0115</v>
+        <v>-3.8439</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7719</v>
+        <v>2.8943</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2396</v>
+        <v>-6.7382</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.6686</v>
+        <v>6.0701</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.1046</v>
+        <v>1.598</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4360000000000001</v>
+        <v>4.4722</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7684</v>
+        <v>7.351599999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.0722</v>
+        <v>1.178</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3037</v>
+        <v>6.1736</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9002</v>
+        <v>-1.2815</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0324</v>
+        <v>0.4200999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1322</v>
+        <v>-1.7015</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.423</v>
+        <v>-0.8811</v>
       </c>
       <c r="Q8" t="n">
         <v>-3.5244</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1013</v>
+        <v>2.6432</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5665</v>
+        <v>-1.2826</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6575</v>
+        <v>-0.9328</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9087999999999999</v>
+        <v>-0.3496</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4863999999999999</v>
+        <v>-7.7503</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8634</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3497</v>
+        <v>-7.7503</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.1265</v>
+        <v>-5.2147</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5416</v>
+        <v>-0.09529999999999994</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.668</v>
+        <v>-5.1194</v>
       </c>
       <c r="G9" t="n">
-        <v>6.0701</v>
+        <v>0.1061000000000005</v>
       </c>
       <c r="H9" t="n">
-        <v>1.598</v>
+        <v>2.5507</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4722</v>
+        <v>-2.4447</v>
       </c>
       <c r="J9" t="n">
-        <v>7.351599999999999</v>
+        <v>2.8843</v>
       </c>
       <c r="K9" t="n">
-        <v>1.178</v>
+        <v>3.2477</v>
       </c>
       <c r="L9" t="n">
-        <v>6.1736</v>
+        <v>-0.3634</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2815</v>
+        <v>-2.7782</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4200999999999999</v>
+        <v>-0.6969999999999998</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7015</v>
+        <v>-2.0813</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8811</v>
+        <v>-1.3216</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.5244</v>
+        <v>-5.5069</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6432</v>
+        <v>4.1852</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.5652</v>
+        <v>0.6704</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.2858</v>
+        <v>1.2323</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2796</v>
+        <v>-0.5618</v>
       </c>
       <c r="V9" t="n">
-        <v>-7.7503</v>
+        <v>-4.6695</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.295</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.7503</v>
+        <v>-5.9645</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.4127</v>
+        <v>-5.638400000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.340800000000001</v>
+        <v>-7.255100000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.07180000000000009</v>
+        <v>1.6166</v>
       </c>
       <c r="G10" t="n">
-        <v>5.667</v>
+        <v>-5.5568</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.137600000000001</v>
+        <v>-1.2456</v>
       </c>
       <c r="I10" t="n">
-        <v>9.804600000000001</v>
+        <v>-4.3111</v>
       </c>
       <c r="J10" t="n">
-        <v>9.7738</v>
+        <v>-5.1947</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.5013</v>
+        <v>-0.9317</v>
       </c>
       <c r="L10" t="n">
-        <v>13.2751</v>
+        <v>-4.2631</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.1067</v>
+        <v>-0.3621000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6363</v>
+        <v>-0.3139</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.4705</v>
+        <v>-0.04820000000000002</v>
       </c>
       <c r="P10" t="n">
-        <v>-6.6082</v>
+        <v>-3.3042</v>
       </c>
       <c r="Q10" t="n">
-        <v>-14.7582</v>
+        <v>-6.8285</v>
       </c>
       <c r="R10" t="n">
-        <v>8.1502</v>
+        <v>3.5243</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.4257</v>
+        <v>-0.3942000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.8453</v>
+        <v>0.1075</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5804</v>
+        <v>-0.5016999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0458</v>
+        <v>3.6167</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4889</v>
+        <v>4.6607</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5347</v>
+        <v>-1.044</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.6022</v>
+        <v>-6.0375</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.959200000000001</v>
+        <v>-3.2405</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3572</v>
+        <v>-2.7969</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.5568</v>
+        <v>-3.6686</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2456</v>
+        <v>-4.1046</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.3111</v>
+        <v>0.4360000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.1947</v>
+        <v>-1.7684</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9317</v>
+        <v>-2.0722</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.2631</v>
+        <v>0.3037</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3621000000000001</v>
+        <v>-1.9002</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3139</v>
+        <v>-2.0324</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.04820000000000002</v>
+        <v>0.1322</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.3042</v>
+        <v>-2.423</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.8285</v>
+        <v>-3.5244</v>
       </c>
       <c r="R11" t="n">
-        <v>3.5243</v>
+        <v>1.1013</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3578</v>
+        <v>0.5405</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5968</v>
+        <v>0.1889</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7611000000000001</v>
+        <v>0.3516</v>
       </c>
       <c r="V11" t="n">
-        <v>3.6167</v>
+        <v>-0.4863999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>4.6607</v>
+        <v>1.8634</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.044</v>
+        <v>-2.3497</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.4764</v>
+        <v>-14.8864</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.7744</v>
+        <v>-11.0524</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.702</v>
+        <v>-3.834</v>
       </c>
       <c r="G12" t="n">
         <v>-11.3576</v>
@@ -1390,13 +1390,13 @@
         <v>4.6258</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9825</v>
+        <v>0.5726</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5009</v>
+        <v>1.223</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5183</v>
+        <v>-0.6503</v>
       </c>
       <c r="V12" t="n">
         <v>-4.1012</v>
@@ -1423,16 +1423,16 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-29.9765</v>
+        <v>-25.3345</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.1611</v>
+        <v>-11.5212</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.8151</v>
+        <v>-13.8137</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.7284</v>
+        <v>-4.728399999999997</v>
       </c>
       <c r="H13" t="n">
         <v>-5.5094</v>
@@ -1441,7 +1441,7 @@
         <v>0.7811000000000021</v>
       </c>
       <c r="J13" t="n">
-        <v>17.6064</v>
+        <v>17.60639999999999</v>
       </c>
       <c r="K13" t="n">
         <v>1.467899999999999</v>
@@ -1450,7 +1450,7 @@
         <v>16.1381</v>
       </c>
       <c r="M13" t="n">
-        <v>-22.33440000000001</v>
+        <v>-22.3344</v>
       </c>
       <c r="N13" t="n">
         <v>-6.977300000000001</v>
@@ -1465,22 +1465,22 @@
         <v>-53.9668</v>
       </c>
       <c r="R13" t="n">
-        <v>52.8656</v>
+        <v>52.86560000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.591700000000001</v>
+        <v>-4.950200000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.4249</v>
+        <v>-1.784</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.1671</v>
+        <v>-3.1653</v>
       </c>
       <c r="V13" t="n">
         <v>-14.5546</v>
       </c>
       <c r="W13" t="n">
-        <v>26.62430000000001</v>
+        <v>26.6243</v>
       </c>
       <c r="X13" t="n">
         <v>-41.1786</v>
